--- a/examples/excel/charts/charts-combo.xlsx
+++ b/examples/excel/charts/charts-combo.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Combo Fundamentals" sheetId="2" r:id="R5218b6c1021c4b64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Combo Styling" sheetId="3" r:id="Rc2c911d238244753"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Combo Advanced" sheetId="4" r:id="Rd203ed19cf9f41c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Combo Effects" sheetId="5" r:id="R3620a72d77114746"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Combo Fundamentals" sheetId="2" r:id="Rb8cd5a43cd514048"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Combo Styling" sheetId="3" r:id="R65c567c689274554"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Combo Advanced" sheetId="4" r:id="R9781294c24684cf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Combo Effects" sheetId="5" r:id="R614d2954b0004eca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -143,6 +143,7 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
@@ -156,9 +157,11 @@
             <c:v>Margin %</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -202,7 +205,6 @@
             </c:numLit>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -323,19 +325,13 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <c:marker val="1"/>
-        <c:axId val="1"/>
-        <c:axId val="2"/>
-      </c:lineChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -343,9 +339,11 @@
             <c:v>Profit %</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -449,7 +447,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -584,19 +582,13 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <c:marker val="1"/>
-        <c:axId val="1"/>
-        <c:axId val="2"/>
-      </c:lineChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
@@ -604,9 +596,11 @@
             <c:v>Delta %</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -704,7 +698,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -756,9 +750,6 @@
               <a:srgbClr val="4472C4"/>
             </a:solidFill>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-          </c:marker>
           <c:cat>
             <c:strLit>
               <c:ptCount val="5"/>
@@ -801,19 +792,13 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <c:marker val="1"/>
-        <c:axId val="1"/>
-        <c:axId val="2"/>
-      </c:lineChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -821,13 +806,12 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-          </c:marker>
           <c:cat>
             <c:strLit>
               <c:ptCount val="5"/>
@@ -877,13 +861,12 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-          </c:marker>
           <c:cat>
             <c:strLit>
               <c:ptCount val="5"/>
@@ -933,13 +916,12 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-          </c:marker>
           <c:cat>
             <c:strLit>
               <c:ptCount val="5"/>
@@ -1042,7 +1024,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -1202,6 +1184,7 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
@@ -1215,9 +1198,11 @@
             <c:v>Ratio</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -1261,7 +1246,6 @@
             </c:numLit>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -1429,6 +1413,7 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
@@ -1442,9 +1427,11 @@
             <c:v>Margin %</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="548235"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -1482,7 +1469,6 @@
             </c:numLit>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -1663,6 +1649,7 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
@@ -1676,9 +1663,11 @@
             <c:v>Target</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:dPt>
             <c:idx val="0"/>
@@ -1762,7 +1751,6 @@
             </c:numLit>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -2060,12 +2048,6 @@
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <c:axId val="1"/>
-        <c:axId val="2"/>
-      </c:lineChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="4"/>
           <c:order val="4"/>
@@ -2073,9 +2055,11 @@
             <c:v>Margin %</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -2187,7 +2171,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -2232,7 +2216,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Sales ()</c:v>
+            <c:v>Sales ($K)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2281,19 +2265,13 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <c:marker val="1"/>
-        <c:axId val="1"/>
-        <c:axId val="2"/>
-      </c:lineChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -2301,9 +2279,11 @@
             <c:v>Growth %</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -2403,7 +2383,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US" sz="1400" b="1"/>
-                  <a:t>Sales ()</a:t>
+                  <a:t>Sales ($K)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2443,7 +2423,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -2603,9 +2583,11 @@
             <c:v>Trend</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -2893,12 +2875,6 @@
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <c:axId val="1"/>
-        <c:axId val="2"/>
-      </c:lineChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
@@ -2906,9 +2882,11 @@
             <c:v>Net Margin %</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -3030,7 +3008,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -3171,6 +3149,7 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
@@ -3184,9 +3163,11 @@
             <c:v>Profit %</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -3224,7 +3205,6 @@
             </c:numLit>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -3475,6 +3455,7 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
@@ -3488,9 +3469,11 @@
             <c:v>Variance</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="A5A5A5"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="50800" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -3541,7 +3524,6 @@
             </c:numLit>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -3682,12 +3664,62 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
         </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Avg Price</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>Q1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Q2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Q3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Q4</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>48</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>52</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>55</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
         <c:dLbls>
           <c:txPr>
             <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
@@ -3702,66 +3734,14 @@
               </a:pPr>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
-        <c:axId val="1"/>
-        <c:axId val="2"/>
-      </c:lineChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Avg Price</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
-          </c:spPr>
-          <c:cat>
-            <c:strLit>
-              <c:ptCount val="4"/>
-              <c:pt idx="0">
-                <c:v>Q1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>Q2</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>Q3</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>Q4</c:v>
-              </c:pt>
-            </c:strLit>
-          </c:cat>
-          <c:val>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="4"/>
-              <c:pt idx="0">
-                <c:v>45</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>48</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>52</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>55</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:val>
-        </c:ser>
         <c:axId val="3"/>
         <c:axId val="4"/>
       </c:lineChart>
@@ -3822,7 +3802,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -3970,6 +3950,7 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
@@ -3983,9 +3964,11 @@
             <c:v>Growth %</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -4029,7 +4012,6 @@
             </c:numLit>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -4166,6 +4148,7 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
@@ -4179,9 +4162,11 @@
             <c:v>Forecast</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="BDD7EE"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="BDD7EE"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -4264,7 +4249,6 @@
             </c:numLit>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -4345,7 +4329,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R140083505edb4fc5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R64dc1dd59d6345ef"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4375,7 +4359,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7ae1f5ff28584b62"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5707963c849b461d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4405,7 +4389,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1c42431c95684a7b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R967b697e220a42a1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4435,7 +4419,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9c8f247fd8484eb2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ce6509f8096439d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4470,7 +4454,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8a75addc2bac4cbe"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R66424c4546d840db"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4500,7 +4484,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc38be8624f4d4a05"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Red997bf020e74835"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4530,7 +4514,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R90383644e0634d91"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R26a214b8b22b4539"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4560,7 +4544,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R78ec45e610874d81"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rabb34ae5a0c643b1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4595,7 +4579,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbd915e8dc53c42b7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2f95301aadac4a19"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4625,7 +4609,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R607648716c164c54"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9f764fbb5c314352"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4655,7 +4639,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R04c542f39c444ea7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rda5960a3ced54dbc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4685,7 +4669,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdb823e46da4142bb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf6324f8680ca4eff"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4720,7 +4704,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R40ba4e5ecd0944cc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfde234b3ec1e4b3d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4750,7 +4734,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8a5432263615426a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf6ac396ec18e4d61"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4780,7 +4764,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf22fda45259a4843"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R68c306b9c14141d2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4810,7 +4794,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0bf7e9e57feb432f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3b0c913830504c38"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4819,30 +4803,139 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racbdac32730146e3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7c9ebd7d10046c5"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8106ea39f0b24985"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38fc65ad6c294513"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae926367dc2247df"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra336bd3ced614257"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c64734edaed42ad"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc548877befc41b9"/>
 </x:worksheet>
 </file>